--- a/Data/C13 Figures.xlsx
+++ b/Data/C13 Figures.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="145" uniqueCount="145">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -447,6 +447,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jun 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Jul 2026</t>
   </si>
 </sst>
 </file>
@@ -4007,6 +4010,29 @@
         <v>0.00830592670669574</v>
       </c>
     </row>
+    <row r="140">
+      <c r="A140" t="s">
+        <v>145</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.0303214069132807</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.0110868026821156</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.00287521461726805</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.00342527033571947</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.00327325364843684</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.00966086562974072</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/Data/C13 Figures.xlsx
+++ b/Data/C13 Figures.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="146" uniqueCount="146">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="147">
   <si>
     <t xml:space="preserve">Date</t>
   </si>
@@ -450,6 +450,9 @@
   </si>
   <si>
     <t xml:space="preserve">Jul 2026</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Aug 2026</t>
   </si>
 </sst>
 </file>
@@ -4033,6 +4036,29 @@
         <v>0.00966086562974072</v>
       </c>
     </row>
+    <row r="141">
+      <c r="A141" t="s">
+        <v>146</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.0303398058252426</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.0117659412773678</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.00344555663737661</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.00303404645784736</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.00304129414275039</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.00905296730990045</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>
